--- a/docs/downloads/20082026Tduh Developer Project Sales Status 13.xlsx
+++ b/docs/downloads/20082026Tduh Developer Project Sales Status 13.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AZ18"/>
+  <dimension ref="A2:BC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -540,6 +540,9 @@
     <col width="9" customWidth="1" min="50" max="50"/>
     <col width="9" customWidth="1" min="51" max="51"/>
     <col width="9" customWidth="1" min="52" max="52"/>
+    <col width="9" customWidth="1" min="53" max="53"/>
+    <col width="9" customWidth="1" min="54" max="54"/>
+    <col width="9" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -600,8 +603,11 @@
       <c r="AU3" s="3" t="n">
         <v>46241</v>
       </c>
-      <c r="AX3" s="4" t="n">
+      <c r="AX3" s="3" t="n">
         <v>46248</v>
+      </c>
+      <c r="BA3" s="4" t="n">
+        <v>46255</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -852,17 +858,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="AX4" s="6" t="inlineStr">
+      <c r="AX4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="AY4" s="6" t="inlineStr">
+      <c r="AY4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AZ4" s="6" t="inlineStr">
+      <c r="AZ4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BA4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="BB4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BC4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -934,12 +955,23 @@
       <c r="AU5" s="9" t="n"/>
       <c r="AV5" s="9" t="n"/>
       <c r="AW5" s="10" t="n"/>
-      <c r="AX5" s="11" t="n"/>
-      <c r="AY5" s="11" t="n">
+      <c r="AX5" s="9" t="n"/>
+      <c r="AY5" s="9" t="n">
         <v>177</v>
       </c>
-      <c r="AZ5" s="12">
+      <c r="AZ5" s="10">
         <f>AY5/$E$5</f>
+        <v/>
+      </c>
+      <c r="BA5" s="11">
+        <f>BB5-AY5</f>
+        <v/>
+      </c>
+      <c r="BB5" s="11" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC5" s="12">
+        <f>BB5/$E$5</f>
         <v/>
       </c>
     </row>
@@ -1126,15 +1158,26 @@
         <f>AV6/$E$6</f>
         <v/>
       </c>
-      <c r="AX6" s="11">
+      <c r="AX6" s="9">
         <f>AY6-AV6</f>
         <v/>
       </c>
-      <c r="AY6" s="11" t="n">
+      <c r="AY6" s="9" t="n">
         <v>334</v>
       </c>
-      <c r="AZ6" s="12">
+      <c r="AZ6" s="10">
         <f>AY6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BA6" s="11">
+        <f>BB6-AY6</f>
+        <v/>
+      </c>
+      <c r="BB6" s="11" t="n">
+        <v>344</v>
+      </c>
+      <c r="BC6" s="12">
+        <f>BB6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -1322,15 +1365,26 @@
         <f>AV7/$E$7</f>
         <v/>
       </c>
-      <c r="AX7" s="11">
+      <c r="AX7" s="9">
         <f>AY7-AV7</f>
         <v/>
       </c>
-      <c r="AY7" s="11" t="n">
+      <c r="AY7" s="9" t="n">
         <v>119</v>
       </c>
-      <c r="AZ7" s="12">
+      <c r="AZ7" s="10">
         <f>AY7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BA7" s="11">
+        <f>BB7-AY7</f>
+        <v/>
+      </c>
+      <c r="BB7" s="11" t="n">
+        <v>123</v>
+      </c>
+      <c r="BC7" s="12">
+        <f>BB7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -1517,15 +1571,26 @@
         <f>AV8/$E$8</f>
         <v/>
       </c>
-      <c r="AX8" s="11">
+      <c r="AX8" s="9">
         <f>AY8-AV8</f>
         <v/>
       </c>
-      <c r="AY8" s="11" t="n">
+      <c r="AY8" s="9" t="n">
         <v>996</v>
       </c>
-      <c r="AZ8" s="12">
+      <c r="AZ8" s="10">
         <f>AY8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BA8" s="11">
+        <f>BB8-AY8</f>
+        <v/>
+      </c>
+      <c r="BB8" s="11" t="n">
+        <v>1003</v>
+      </c>
+      <c r="BC8" s="12">
+        <f>BB8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -1713,15 +1778,26 @@
         <f>AV9/$E$9</f>
         <v/>
       </c>
-      <c r="AX9" s="11">
+      <c r="AX9" s="9">
         <f>AY9-AV9</f>
         <v/>
       </c>
-      <c r="AY9" s="11" t="n">
+      <c r="AY9" s="9" t="n">
         <v>1125</v>
       </c>
-      <c r="AZ9" s="12">
+      <c r="AZ9" s="10">
         <f>AY9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BA9" s="11">
+        <f>BB9-AY9</f>
+        <v/>
+      </c>
+      <c r="BB9" s="11" t="n">
+        <v>1125</v>
+      </c>
+      <c r="BC9" s="12">
+        <f>BB9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -1909,15 +1985,26 @@
         <f>AV10/$E$10</f>
         <v/>
       </c>
-      <c r="AX10" s="11">
+      <c r="AX10" s="9">
         <f>AY10-AV10</f>
         <v/>
       </c>
-      <c r="AY10" s="11" t="n">
+      <c r="AY10" s="9" t="n">
         <v>499</v>
       </c>
-      <c r="AZ10" s="12">
+      <c r="AZ10" s="10">
         <f>AY10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BA10" s="11">
+        <f>BB10-AY10</f>
+        <v/>
+      </c>
+      <c r="BB10" s="11" t="n">
+        <v>509</v>
+      </c>
+      <c r="BC10" s="12">
+        <f>BB10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -2104,15 +2191,26 @@
         <f>AV11/$E$11</f>
         <v/>
       </c>
-      <c r="AX11" s="11">
+      <c r="AX11" s="9">
         <f>AY11-AV11</f>
         <v/>
       </c>
-      <c r="AY11" s="11" t="n">
+      <c r="AY11" s="9" t="n">
         <v>467</v>
       </c>
-      <c r="AZ11" s="12">
+      <c r="AZ11" s="10">
         <f>AY11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BA11" s="11">
+        <f>BB11-AY11</f>
+        <v/>
+      </c>
+      <c r="BB11" s="11" t="n">
+        <v>467</v>
+      </c>
+      <c r="BC11" s="12">
+        <f>BB11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -2299,15 +2397,26 @@
         <f>AV12/$E$12</f>
         <v/>
       </c>
-      <c r="AX12" s="11">
+      <c r="AX12" s="9">
         <f>AY12-AV12</f>
         <v/>
       </c>
-      <c r="AY12" s="11" t="n">
+      <c r="AY12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="AZ12" s="12">
+      <c r="AZ12" s="10">
         <f>AY12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BA12" s="11">
+        <f>BB12-AY12</f>
+        <v/>
+      </c>
+      <c r="BB12" s="11" t="n">
+        <v>236</v>
+      </c>
+      <c r="BC12" s="12">
+        <f>BB12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -2495,15 +2604,26 @@
         <f>AV13/$E$13</f>
         <v/>
       </c>
-      <c r="AX13" s="11">
+      <c r="AX13" s="9">
         <f>AY13-AV13</f>
         <v/>
       </c>
-      <c r="AY13" s="11" t="n">
+      <c r="AY13" s="9" t="n">
         <v>618</v>
       </c>
-      <c r="AZ13" s="12">
+      <c r="AZ13" s="10">
         <f>AY13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BA13" s="11">
+        <f>BB13-AY13</f>
+        <v/>
+      </c>
+      <c r="BB13" s="11" t="n">
+        <v>626</v>
+      </c>
+      <c r="BC13" s="12">
+        <f>BB13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -2690,15 +2810,26 @@
         <f>AV14/$E$14</f>
         <v/>
       </c>
-      <c r="AX14" s="11">
+      <c r="AX14" s="9">
         <f>AY14-AV14</f>
         <v/>
       </c>
-      <c r="AY14" s="11" t="n">
+      <c r="AY14" s="9" t="n">
         <v>1142</v>
       </c>
-      <c r="AZ14" s="12">
+      <c r="AZ14" s="10">
         <f>AY14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BA14" s="11">
+        <f>BB14-AY14</f>
+        <v/>
+      </c>
+      <c r="BB14" s="11" t="n">
+        <v>1151</v>
+      </c>
+      <c r="BC14" s="12">
+        <f>BB14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -2885,15 +3016,26 @@
         <f>AV15/$E$15</f>
         <v/>
       </c>
-      <c r="AX15" s="11">
+      <c r="AX15" s="9">
         <f>AY15-AV15</f>
         <v/>
       </c>
-      <c r="AY15" s="11" t="n">
+      <c r="AY15" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="AZ15" s="12">
+      <c r="AZ15" s="10">
         <f>AY15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BA15" s="11">
+        <f>BB15-AY15</f>
+        <v/>
+      </c>
+      <c r="BB15" s="11" t="n">
+        <v>127</v>
+      </c>
+      <c r="BC15" s="12">
+        <f>BB15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -3016,15 +3158,26 @@
         <f>AV16/$E$16</f>
         <v/>
       </c>
-      <c r="AX16" s="11">
+      <c r="AX16" s="9">
         <f>AY16-AV16</f>
         <v/>
       </c>
-      <c r="AY16" s="11" t="n">
+      <c r="AY16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AZ16" s="12">
+      <c r="AZ16" s="10">
         <f>AY16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BA16" s="11">
+        <f>BB16-AY16</f>
+        <v/>
+      </c>
+      <c r="BB16" s="11" t="n">
+        <v>659</v>
+      </c>
+      <c r="BC16" s="12">
+        <f>BB16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -3090,9 +3243,12 @@
       <c r="AU17" s="9" t="n"/>
       <c r="AV17" s="9" t="n"/>
       <c r="AW17" s="10" t="n"/>
-      <c r="AX17" s="11" t="n"/>
-      <c r="AY17" s="11" t="n"/>
-      <c r="AZ17" s="12" t="n"/>
+      <c r="AX17" s="9" t="n"/>
+      <c r="AY17" s="9" t="n"/>
+      <c r="AZ17" s="10" t="n"/>
+      <c r="BA17" s="11" t="n"/>
+      <c r="BB17" s="11" t="n"/>
+      <c r="BC17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3160,19 +3316,31 @@
       <c r="AU18" s="9" t="n"/>
       <c r="AV18" s="9" t="n"/>
       <c r="AW18" s="10" t="n"/>
-      <c r="AX18" s="11" t="n"/>
-      <c r="AY18" s="11" t="n">
+      <c r="AX18" s="9" t="n"/>
+      <c r="AY18" s="9" t="n">
         <v>139</v>
       </c>
-      <c r="AZ18" s="12">
+      <c r="AZ18" s="10">
         <f>AY18/$E$18</f>
+        <v/>
+      </c>
+      <c r="BA18" s="11">
+        <f>BB18-AY18</f>
+        <v/>
+      </c>
+      <c r="BB18" s="11" t="n">
+        <v>191</v>
+      </c>
+      <c r="BC18" s="12">
+        <f>BB18/$E$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="AU3:AW3"/>
+    <mergeCell ref="BA3:BC3"/>
     <mergeCell ref="W3:Y3"/>
     <mergeCell ref="AR3:AT3"/>
     <mergeCell ref="AI3:AK3"/>
